--- a/toptier/files/TopTier.NetProfit.2025v2026.260831.xlsx
+++ b/toptier/files/TopTier.NetProfit.2025v2026.260831.xlsx
@@ -656,7 +656,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Top Tier Roofing &amp; Remodeling, LLC   |   EIN 99-3048348   |   prepared 31 August 2026</t>
+          <t>Top Tier Roofing &amp; Remodeling, LLC   |   prepared 31 August 2026</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Top Tier Roofing &amp; Remodeling, LLC   |   EIN 99-3048348   |   prepared 31 August 2026</t>
+          <t>Top Tier Roofing &amp; Remodeling, LLC   |   prepared 31 August 2026</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Top Tier Roofing &amp; Remodeling, LLC   |   EIN 99-3048348   |   prepared 31 August 2026</t>
+          <t>Top Tier Roofing &amp; Remodeling, LLC   |   prepared 31 August 2026</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Top Tier Roofing &amp; Remodeling, LLC   |   EIN 99-3048348   |   prepared 31 August 2026</t>
+          <t>Top Tier Roofing &amp; Remodeling, LLC   |   prepared 31 August 2026</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Top Tier Roofing &amp; Remodeling, LLC   |   EIN 99-3048348   |   prepared 31 August 2026</t>
+          <t>Top Tier Roofing &amp; Remodeling, LLC   |   prepared 31 August 2026</t>
         </is>
       </c>
     </row>

--- a/toptier/files/TopTier.NetProfit.2025v2026.260831.xlsx
+++ b/toptier/files/TopTier.NetProfit.2025v2026.260831.xlsx
@@ -4601,7 +4601,7 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">     No taxpayer identification numbers, dates of birth or personal banking details appear anywhere in this workbook. The only identifiers used are the business EIN and the Minnesota business tax identification number.</t>
+          <t xml:space="preserve">     No taxpayer identification numbers, dates of birth, account numbers or other personal or account identifiers appear anywhere in this workbook.</t>
         </is>
       </c>
     </row>
